--- a/testdata/HotelData.xlsx
+++ b/testdata/HotelData.xlsx
@@ -23,7 +23,7 @@
     <t>Kingfisher Nest Hotel Suites</t>
   </si>
   <si>
-    <t>₹8,977</t>
+    <t>₹8,964</t>
   </si>
   <si>
     <t>Cloud Hotel &amp; Suites</t>
@@ -95,6 +95,9 @@
     <t>Longonot Place Serviced Apartments- Nairobi, City Centre CBD</t>
   </si>
   <si>
+    <t>GemSuites Hotel &amp; Apartments, Riverside</t>
+  </si>
+  <si>
     <t>Villa Leone</t>
   </si>
   <si>
@@ -114,9 +117,6 @@
   </si>
   <si>
     <t>Fairmont The Norfolk</t>
-  </si>
-  <si>
-    <t>Bidwood Suite Hotel</t>
   </si>
 </sst>
 </file>
